--- a/Input_files_LIM/LIM_compartments.xlsx
+++ b/Input_files_LIM/LIM_compartments.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ugentbe-my.sharepoint.com/personal/abril_reynescardona_ugent_be/Documents/UGent-PC/Areynesc/Documents/phD/WP1_TemporalFW/manuscript/Suppl_mat/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ugentbe-my.sharepoint.com/personal/abril_reynescardona_ugent_be/Documents/UGent-PC/Areynesc/Documents/phD/WP1_TemporalFW/manuscript/github_repo/manuscript/Input_files_LIM/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="191" documentId="11_F25DC773A252ABDACC10484619D8444A5BDE58F6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C3E7F9A-7437-40C3-910C-B3AFB637C3D5}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stock data" sheetId="2" r:id="rId1"/>
